--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93400</v>
+        <v>93405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80539</v>
+        <v>80541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93412</v>
+        <v>93418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93418</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93424</v>
+        <v>93437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136722457</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136722454</v>
       </c>
       <c r="B15" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136722459</v>
       </c>
       <c r="B16" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136722493</v>
       </c>
       <c r="B17" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>136722456</v>
       </c>
       <c r="B18" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 11548-2023 artfynd.xlsx
+++ b/artfynd/A 11548-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136722483</v>
       </c>
       <c r="B3" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136722477</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136722460</v>
       </c>
       <c r="B5" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>136722484</v>
       </c>
       <c r="B6" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136722478</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136722481</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>136722455</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>136722458</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>136722480</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136722482</v>
       </c>
       <c r="B12" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136722494</v>
       </c>
       <c r="B13" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136722495</v>
       </c>
       <c r="B14" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
